--- a/results/calibration_results_mqt_llava.xlsx
+++ b/results/calibration_results_mqt_llava.xlsx
@@ -1052,16 +1052,16 @@
         </is>
       </c>
       <c r="C7" s="9" t="n">
-        <v>0.0583130526896114</v>
+        <v>0.0410023931705083</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.0594891243064499</v>
+        <v>0.0509356945512108</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.8199079401611048</v>
+        <v>0.819620253164557</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0.0988138266975547</v>
+        <v>0.1002976195749488</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1">
@@ -1100,16 +1100,16 @@
         </is>
       </c>
       <c r="C9" s="9" t="n">
-        <v>0.0544393612663388</v>
+        <v>0.0441436354249884</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.0713713619601949</v>
+        <v>0.048201220049311</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>0.8164556962025317</v>
+        <v>0.8154200230149596</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>0.100324255635607</v>
+        <v>0.1004788745371115</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1">
@@ -1396,16 +1396,16 @@
         </is>
       </c>
       <c r="C7" s="9" t="n">
-        <v>0.0388074343894967</v>
+        <v>0.0508745672310342</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.0494656320108045</v>
+        <v>0.0509293888243708</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.7811554151862088</v>
+        <v>0.7826556125806027</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0.1797068641076777</v>
+        <v>0.1791193313779527</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1">
@@ -1444,16 +1444,16 @@
         </is>
       </c>
       <c r="C9" s="9" t="n">
-        <v>0.0551737354412495</v>
+        <v>0.0478811463523285</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.0551157521427839</v>
+        <v>0.0550141025514605</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>0.7788393209632847</v>
+        <v>0.7778918278720885</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>0.1826064795796357</v>
+        <v>0.1828052454042991</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1">
@@ -1740,16 +1740,16 @@
         </is>
       </c>
       <c r="C7" s="9" t="n">
-        <v>0.06629721902310839</v>
+        <v>0.0610197532922029</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.0731964475661516</v>
+        <v>0.09650752581655971</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.7445798727213891</v>
+        <v>0.7458742314744904</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0.1950470785674399</v>
+        <v>0.1947175172768888</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1">
@@ -1788,16 +1788,16 @@
         </is>
       </c>
       <c r="C9" s="9" t="n">
-        <v>0.0741705605072811</v>
+        <v>0.0706533397074416</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.0938264417496134</v>
+        <v>0.0637843940173554</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>0.73929457447956</v>
+        <v>0.7373530363499083</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>0.1973232706142787</v>
+        <v>0.1971892652814414</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1">
@@ -2084,16 +2084,16 @@
         </is>
       </c>
       <c r="C7" s="9" t="n">
-        <v>0.0642934729196131</v>
+        <v>0.0629102133288979</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.0672390531934797</v>
+        <v>0.075398990444839</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.7620559704096587</v>
+        <v>0.7282085281596762</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0.1800036825960321</v>
+        <v>0.1910759499467099</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1">
@@ -2132,16 +2132,16 @@
         </is>
       </c>
       <c r="C9" s="9" t="n">
-        <v>0.0773802743585205</v>
+        <v>0.08681627283809</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.0832186683469736</v>
+        <v>0.08616621487158831</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>0.7193628306232116</v>
+        <v>0.7067834461581408</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>0.2006647812318973</v>
+        <v>0.2066271560528332</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1">
@@ -2428,16 +2428,16 @@
         </is>
       </c>
       <c r="C7" s="9" t="n">
-        <v>0.0599342763237655</v>
+        <v>0.0581201290525496</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.0476276184730231</v>
+        <v>0.0681364729441702</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.799400074990626</v>
+        <v>0.7987604490615144</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0.1439245914963808</v>
+        <v>0.1471212720920504</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1">
@@ -2476,16 +2476,16 @@
         </is>
       </c>
       <c r="C9" s="9" t="n">
-        <v>0.0607559235325155</v>
+        <v>0.060693861204388</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.0561883278728386</v>
+        <v>0.0518203402546</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>0.8033701669644235</v>
+        <v>0.8028628774344384</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>0.1471075545473904</v>
+        <v>0.1476153836576534</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1">
@@ -2772,16 +2772,16 @@
         </is>
       </c>
       <c r="C7" s="9" t="n">
-        <v>0.0833563949167728</v>
+        <v>0.079640741944313</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.09814904376864431</v>
+        <v>0.06675517082214349</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.7890625</v>
+        <v>0.786047149122807</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0.1531753090910079</v>
+        <v>0.1522054591253214</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1">
@@ -2820,16 +2820,16 @@
         </is>
       </c>
       <c r="C9" s="9" t="n">
-        <v>0.0995884422859859</v>
+        <v>0.1029983350152124</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.1129910840653996</v>
+        <v>0.1178951459657736</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>0.7582236842105263</v>
+        <v>0.7582236842105262</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>0.1544681291608227</v>
+        <v>0.1548432009541706</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1">
@@ -3116,16 +3116,16 @@
         </is>
       </c>
       <c r="C7" s="9" t="n">
-        <v>0.0999967803806066</v>
+        <v>0.1466089357435703</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.127762721851468</v>
+        <v>0.1248133246600628</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.6996281780725554</v>
+        <v>0.6973168525776303</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0.2193190038540945</v>
+        <v>0.2179411001471734</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1">
@@ -3164,16 +3164,16 @@
         </is>
       </c>
       <c r="C9" s="9" t="n">
-        <v>0.0788453392042833</v>
+        <v>0.0866259112146021</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.1482285052203004</v>
+        <v>0.1136475044703896</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>0.7065621545573308</v>
+        <v>0.7031454125213547</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>0.2168679143062122</v>
+        <v>0.2169136219797841</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1">
@@ -3460,16 +3460,16 @@
         </is>
       </c>
       <c r="C7" s="9" t="n">
-        <v>0.0197417381592094</v>
+        <v>0.0237031287234276</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.0630647279508412</v>
+        <v>0.0680168697517365</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.7129724208375894</v>
+        <v>0.7060776302349336</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0.0920511794890066</v>
+        <v>0.0919566707280798</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1">
@@ -3508,16 +3508,16 @@
         </is>
       </c>
       <c r="C9" s="9" t="n">
-        <v>0.008407225502152</v>
+        <v>0.0085364383743496</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.06590136204560661</v>
+        <v>0.0475818804657588</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>0.5257916241062308</v>
+        <v>0.526046986721144</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>0.0977322846840494</v>
+        <v>0.0976951118698821</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1">
@@ -3804,16 +3804,16 @@
         </is>
       </c>
       <c r="C7" s="9" t="n">
-        <v>0.0208779350668191</v>
+        <v>0.0079179805493913</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.0313366661220789</v>
+        <v>0.0359506660164333</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.7838541666666666</v>
+        <v>0.6809895833333334</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0.0364641793902275</v>
+        <v>0.0372502280520649</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1">
@@ -3852,16 +3852,16 @@
         </is>
       </c>
       <c r="C9" s="9" t="n">
-        <v>0.0044664794505417</v>
+        <v>0.0047870041851321</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.0437422122210251</v>
+        <v>0.044233617933957</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>0.6647135416666666</v>
+        <v>0.6536458333333334</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>0.0381078883523488</v>
+        <v>0.0382138886525495</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1">
@@ -4148,16 +4148,16 @@
         </is>
       </c>
       <c r="C7" s="9" t="n">
-        <v>0.1012242549657821</v>
+        <v>0.1358867061138153</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.0997575369477272</v>
+        <v>0.1394325536489486</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.7599291957074897</v>
+        <v>0.7630268835048125</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0.1856589764457864</v>
+        <v>0.1851498935135805</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1">
@@ -4196,16 +4196,16 @@
         </is>
       </c>
       <c r="C9" s="9" t="n">
-        <v>0.0840136812430803</v>
+        <v>0.08804219851737891</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.1044554283762782</v>
+        <v>0.11402422638742</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>0.7569421396172142</v>
+        <v>0.7588228786370174</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>0.1860506845216237</v>
+        <v>0.1856269967191408</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1">
@@ -4492,16 +4492,16 @@
         </is>
       </c>
       <c r="C7" s="9" t="n">
-        <v>0.0031846814224627</v>
+        <v>0.003331033450122</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.0107612993748989</v>
+        <v>0.0110316206445349</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.9045226130653268</v>
+        <v>0.9246231155778896</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0.0049304604007795</v>
+        <v>0.004926761724516</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1">
@@ -4540,16 +4540,16 @@
         </is>
       </c>
       <c r="C9" s="9" t="n">
-        <v>0.00285456811362</v>
+        <v>0.002851811630668</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.0110388510243721</v>
+        <v>0.0110376916628278</v>
       </c>
       <c r="E9" s="10" t="n">
         <v>0.7688442211055276</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>0.0049640651267491</v>
+        <v>0.0049638179474554</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1">
@@ -4836,16 +4836,16 @@
         </is>
       </c>
       <c r="C7" s="9" t="n">
-        <v>0.0663138335105031</v>
+        <v>0.0569414038583636</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.08016392693854869</v>
+        <v>0.0807035791501403</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.5756595636732623</v>
+        <v>0.6068619989852866</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0.1942977185809413</v>
+        <v>0.1919447720200565</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1">
@@ -4884,16 +4884,16 @@
         </is>
       </c>
       <c r="C9" s="9" t="n">
-        <v>0.0183487157798349</v>
+        <v>0.0716176666802549</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.1041933760173994</v>
+        <v>0.0941695692221126</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>0.6021689497716896</v>
+        <v>0.6253805175038052</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>0.195548657464131</v>
+        <v>0.1949381057278232</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1">
@@ -5180,16 +5180,16 @@
         </is>
       </c>
       <c r="C7" s="9" t="n">
-        <v>0.07554483987390991</v>
+        <v>0.0988146635144948</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.0524315456300973</v>
+        <v>0.101072022691369</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.8428413691571587</v>
+        <v>0.8265243528401423</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0.1445291167400114</v>
+        <v>0.150189118132016</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1">
@@ -5228,16 +5228,16 @@
         </is>
       </c>
       <c r="C9" s="9" t="n">
-        <v>0.07436075835952501</v>
+        <v>0.0645934361022398</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.0658335538741658</v>
+        <v>0.0765615209951442</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>0.831186357502147</v>
+        <v>0.8293460925039873</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>0.1482498223664965</v>
+        <v>0.1497677627607748</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1">
@@ -5524,16 +5524,16 @@
         </is>
       </c>
       <c r="C7" s="9" t="n">
-        <v>0.0021299556219039</v>
+        <v>0.0013724636805289</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.0204510105365845</v>
+        <v>0.0203892592579968</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.7441176470588236</v>
+        <v>0.7147058823529411</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0.0116029909226244</v>
+        <v>0.0115973741692124</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1">
@@ -5572,16 +5572,16 @@
         </is>
       </c>
       <c r="C9" s="9" t="n">
-        <v>0.0015056360352686</v>
+        <v>0.0015058123109828</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.0214591675211905</v>
+        <v>0.0214586836847313</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>0.3441176470588235</v>
+        <v>0.3470588235294117</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>0.0115155715525601</v>
+        <v>0.0115155400888486</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1">
